--- a/manuscript/Table-2.xlsx
+++ b/manuscript/Table-2.xlsx
@@ -388,11 +388,11 @@
         </is>
       </c>
       <c r="B2">
-        <v>140.11</v>
+        <v>143.83</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -402,22 +402,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.89</t>
+          <t>29.77</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Plant height at 100% maturity</t>
+          <t>Plant height at physiological maturity</t>
         </is>
       </c>
       <c r="B3">
-        <v>205.86</v>
+        <v>210.95</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>24.49</t>
         </is>
       </c>
     </row>
@@ -463,21 +463,21 @@
         </is>
       </c>
       <c r="B5">
-        <v>56.97</v>
+        <v>45.24</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>132.52</t>
+          <t>52.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>9.90</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>14.41</v>
+        <v>12.97</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -497,19 +497,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>137.84</t>
+          <t>33.91</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>105.84</t>
+          <t>51.72</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Days to flowering</t>
+          <t>Days to 50% flowering</t>
         </is>
       </c>
       <c r="B7">
@@ -563,21 +563,21 @@
         </is>
       </c>
       <c r="B9">
-        <v>14.14</v>
+        <v>13.86</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>17.68</t>
         </is>
       </c>
     </row>
@@ -663,21 +663,21 @@
         </is>
       </c>
       <c r="B13">
-        <v>15.89</v>
+        <v>15.76</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.88</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>19.94</t>
         </is>
       </c>
     </row>

--- a/manuscript/Table-2.xlsx
+++ b/manuscript/Table-2.xlsx
@@ -388,21 +388,21 @@
         </is>
       </c>
       <c r="B2">
-        <v>143.83</v>
+        <v>145.17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>225.00</t>
+          <t>225.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.76</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>210.95</v>
+        <v>212.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -427,7 +427,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>24.11</t>
         </is>
       </c>
     </row>
@@ -438,7 +438,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>11.35</v>
+        <v>11.11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -452,7 +452,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.42</t>
+          <t>58.77</t>
         </is>
       </c>
     </row>
@@ -463,21 +463,21 @@
         </is>
       </c>
       <c r="B5">
-        <v>45.24</v>
+        <v>45.34</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>33.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.91</t>
+          <t>52.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>9.91</t>
         </is>
       </c>
     </row>
@@ -488,21 +488,21 @@
         </is>
       </c>
       <c r="B6">
-        <v>12.97</v>
+        <v>13.17</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.91</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>51.52</t>
         </is>
       </c>
     </row>
@@ -513,21 +513,21 @@
         </is>
       </c>
       <c r="B7">
-        <v>88.84</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.19</t>
+          <t>68.04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>238.15</t>
+          <t>238.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>23.22</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>18.94</v>
+        <v>18.92</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>19.20</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>13.86</v>
+        <v>13.84</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -572,12 +572,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>18.37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>18.55</t>
         </is>
       </c>
     </row>
@@ -588,21 +588,21 @@
         </is>
       </c>
       <c r="B10">
-        <v>95.40000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15.91</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>389.83</t>
+          <t>390.68</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.01</t>
+          <t>78.47</t>
         </is>
       </c>
     </row>
@@ -613,21 +613,21 @@
         </is>
       </c>
       <c r="B11">
-        <v>192.45</v>
+        <v>191.38</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>148.00</t>
+          <t>148.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>247.00</t>
+          <t>247.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>11.77</t>
         </is>
       </c>
     </row>
@@ -638,11 +638,11 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>21.35</t>
         </is>
       </c>
     </row>
@@ -663,21 +663,21 @@
         </is>
       </c>
       <c r="B13">
-        <v>15.76</v>
+        <v>15.69</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>7.36</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22.88</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>20.72</t>
         </is>
       </c>
     </row>

--- a/manuscript/Table-2.xlsx
+++ b/manuscript/Table-2.xlsx
@@ -388,7 +388,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>145.17</v>
+        <v>143.88</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -402,7 +402,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>30.28</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>212.5</v>
+        <v>211.08</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -427,7 +427,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>24.50</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.77</t>
+          <t>58.71</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>45.34</v>
+        <v>45.43</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -477,7 +477,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>9.81</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>13.17</v>
+        <v>13.12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>51.89</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>87.95999999999999</v>
+        <v>87.92</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23.25</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>18.92</v>
+        <v>18.89</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>19.25</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>13.84</v>
+        <v>13.81</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.41</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>96.20999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.47</t>
+          <t>78.03</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>191.38</v>
+        <v>191.23</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -627,7 +627,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.77</t>
+          <t>11.81</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>5.71</v>
+        <v>5.7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.37</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>15.69</v>
+        <v>15.71</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>20.66</t>
         </is>
       </c>
     </row>

--- a/manuscript/Table-2.xlsx
+++ b/manuscript/Table-2.xlsx
@@ -34,10 +34,10 @@
     <t>H2</t>
   </si>
   <si>
-    <t>Plant height at 50% flowering</t>
-  </si>
-  <si>
-    <t>143.76</t>
+    <t>PH50F</t>
+  </si>
+  <si>
+    <t>145.12</t>
   </si>
   <si>
     <t>14.12</t>
@@ -46,16 +46,16 @@
     <t>226.38</t>
   </si>
   <si>
-    <t>30.32</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>Plant height at 90% physiological maturity</t>
-  </si>
-  <si>
-    <t>211.42</t>
+    <t>29.78</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>PH90M</t>
+  </si>
+  <si>
+    <t>212.57</t>
   </si>
   <si>
     <t>31.22</t>
@@ -64,16 +64,16 @@
     <t>288.69</t>
   </si>
   <si>
-    <t>24.39</t>
+    <t>23.98</t>
   </si>
   <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>Stem diameter at 50% flowering</t>
-  </si>
-  <si>
-    <t>10.71</t>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>10.72</t>
   </si>
   <si>
     <t>5.63</t>
@@ -82,181 +82,178 @@
     <t>32.37</t>
   </si>
   <si>
-    <t>51.19</t>
+    <t>51.10</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>SPAD</t>
+  </si>
+  <si>
+    <t>45.33</t>
+  </si>
+  <si>
+    <t>32.92</t>
+  </si>
+  <si>
+    <t>58.86</t>
+  </si>
+  <si>
+    <t>11.20</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>NFC</t>
+  </si>
+  <si>
+    <t>13.17</t>
+  </si>
+  <si>
+    <t>3.61</t>
+  </si>
+  <si>
+    <t>33.53</t>
+  </si>
+  <si>
+    <t>51.98</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>D50F</t>
+  </si>
+  <si>
+    <t>87.71</t>
+  </si>
+  <si>
+    <t>67.00</t>
+  </si>
+  <si>
+    <t>220.00</t>
+  </si>
+  <si>
+    <t>21.39</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>FD</t>
+  </si>
+  <si>
+    <t>18.86</t>
+  </si>
+  <si>
+    <t>12.00</t>
+  </si>
+  <si>
+    <t>30.00</t>
+  </si>
+  <si>
+    <t>17.94</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>13.80</t>
+  </si>
+  <si>
+    <t>7.71</t>
+  </si>
+  <si>
+    <t>19.84</t>
+  </si>
+  <si>
+    <t>18.63</t>
+  </si>
+  <si>
+    <t>NPP</t>
+  </si>
+  <si>
+    <t>96.27</t>
+  </si>
+  <si>
+    <t>10.82</t>
+  </si>
+  <si>
+    <t>397.23</t>
+  </si>
+  <si>
+    <t>78.89</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>D90M</t>
+  </si>
+  <si>
+    <t>191.63</t>
+  </si>
+  <si>
+    <t>148.12</t>
+  </si>
+  <si>
+    <t>247.12</t>
+  </si>
+  <si>
+    <t>12.08</t>
+  </si>
+  <si>
+    <t>NSP</t>
+  </si>
+  <si>
+    <t>5.71</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>8.00</t>
+  </si>
+  <si>
+    <t>21.35</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>15.78</t>
+  </si>
+  <si>
+    <t>6.74</t>
+  </si>
+  <si>
+    <t>22.76</t>
+  </si>
+  <si>
+    <t>19.61</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>95.18</t>
+  </si>
+  <si>
+    <t>20.77</t>
+  </si>
+  <si>
+    <t>150.98</t>
+  </si>
+  <si>
+    <t>25.75</t>
   </si>
   <si>
     <t>0.97</t>
   </si>
   <si>
-    <t>Chlorophyll content (SPAD) at 50% flowering</t>
-  </si>
-  <si>
-    <t>45.45</t>
-  </si>
-  <si>
-    <t>32.92</t>
-  </si>
-  <si>
-    <t>58.86</t>
-  </si>
-  <si>
-    <t>11.01</t>
-  </si>
-  <si>
-    <t>0.33</t>
-  </si>
-  <si>
-    <t>Number of flower clusters per plant</t>
-  </si>
-  <si>
-    <t>13.13</t>
-  </si>
-  <si>
-    <t>3.61</t>
-  </si>
-  <si>
-    <t>33.53</t>
-  </si>
-  <si>
-    <t>52.32</t>
-  </si>
-  <si>
-    <t>0.88</t>
-  </si>
-  <si>
-    <t>Days to 50% flowering</t>
-  </si>
-  <si>
-    <t>87.65</t>
-  </si>
-  <si>
-    <t>67.00</t>
-  </si>
-  <si>
-    <t>220.00</t>
-  </si>
-  <si>
-    <t>21.44</t>
-  </si>
-  <si>
-    <t>0.62</t>
-  </si>
-  <si>
-    <t>Flowering duration (days)</t>
-  </si>
-  <si>
-    <t>18.84</t>
-  </si>
-  <si>
-    <t>12.00</t>
-  </si>
-  <si>
-    <t>30.00</t>
-  </si>
-  <si>
-    <t>18.02</t>
-  </si>
-  <si>
-    <t>Pod length at 90% physiological maturity</t>
-  </si>
-  <si>
-    <t>13.81</t>
-  </si>
-  <si>
-    <t>7.71</t>
-  </si>
-  <si>
-    <t>19.84</t>
-  </si>
-  <si>
-    <t>18.63</t>
-  </si>
-  <si>
-    <t>Number of pods per plant at 90% physiological maturity</t>
-  </si>
-  <si>
-    <t>96.22</t>
-  </si>
-  <si>
-    <t>10.82</t>
-  </si>
-  <si>
-    <t>397.23</t>
-  </si>
-  <si>
-    <t>78.96</t>
-  </si>
-  <si>
-    <t>0.94</t>
-  </si>
-  <si>
-    <t>Days to 90% physiological maturity</t>
-  </si>
-  <si>
-    <t>191.60</t>
-  </si>
-  <si>
-    <t>148.12</t>
-  </si>
-  <si>
-    <t>247.12</t>
-  </si>
-  <si>
-    <t>12.09</t>
-  </si>
-  <si>
-    <t>Number of seeds per pod</t>
-  </si>
-  <si>
-    <t>5.69</t>
-  </si>
-  <si>
-    <t>3.00</t>
-  </si>
-  <si>
-    <t>8.00</t>
-  </si>
-  <si>
-    <t>21.26</t>
-  </si>
-  <si>
-    <t>0.43</t>
-  </si>
-  <si>
-    <t>Pod width at 90% physiological maturity</t>
-  </si>
-  <si>
-    <t>15.79</t>
-  </si>
-  <si>
-    <t>6.74</t>
-  </si>
-  <si>
-    <t>22.76</t>
-  </si>
-  <si>
-    <t>19.56</t>
-  </si>
-  <si>
-    <t>Seed weight</t>
-  </si>
-  <si>
-    <t>95.38</t>
-  </si>
-  <si>
-    <t>20.77</t>
-  </si>
-  <si>
-    <t>150.98</t>
-  </si>
-  <si>
-    <t>25.61</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>Seed length</t>
+    <t>SL</t>
   </si>
   <si>
     <t>15.27</t>
@@ -268,16 +265,16 @@
     <t>21.68</t>
   </si>
   <si>
-    <t>14.87</t>
-  </si>
-  <si>
-    <t>0.95</t>
-  </si>
-  <si>
-    <t>Seed width</t>
-  </si>
-  <si>
-    <t>8.27</t>
+    <t>14.89</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>SWd</t>
+  </si>
+  <si>
+    <t>8.25</t>
   </si>
   <si>
     <t>4.65</t>
@@ -286,13 +283,13 @@
     <t>10.29</t>
   </si>
   <si>
-    <t>14.07</t>
-  </si>
-  <si>
-    <t>Yield per plant</t>
-  </si>
-  <si>
-    <t>288.83</t>
+    <t>14.06</t>
+  </si>
+  <si>
+    <t>YP</t>
+  </si>
+  <si>
+    <t>289.88</t>
   </si>
   <si>
     <t>1.12</t>
@@ -301,13 +298,16 @@
     <t>1082.76</t>
   </si>
   <si>
-    <t>73.58</t>
-  </si>
-  <si>
-    <t>Harvest index</t>
-  </si>
-  <si>
-    <t>42.17</t>
+    <t>73.14</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>42.24</t>
   </si>
   <si>
     <t>21.71</t>
@@ -316,10 +316,10 @@
     <t>80.07</t>
   </si>
   <si>
-    <t>31.87</t>
-  </si>
-  <si>
-    <t>0.77</t>
+    <t>31.85</t>
+  </si>
+  <si>
+    <t>0.80</t>
   </si>
 </sst>
 </file>
@@ -902,24 +902,24 @@
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>70</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>71</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>72</v>
-      </c>
-      <c r="E13" t="s">
-        <v>73</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
@@ -927,59 +927,59 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>75</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>76</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>77</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>78</v>
-      </c>
-      <c r="F14" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
         <v>80</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>81</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>82</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>83</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>84</v>
-      </c>
-      <c r="F15" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
         <v>86</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>87</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>89</v>
-      </c>
-      <c r="E16" t="s">
-        <v>90</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
@@ -987,22 +987,22 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
         <v>91</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>92</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>93</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>94</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>95</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
